--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y91"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: isolated marker/symbol line :: 6</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 9</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -645,7 +649,7 @@
       </c>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | line starts with digit/letter garbage token | suspicious token(s): 1rg (letter/digit mix) :: 1rg ä¸€ 7.</t>
+          <t>L276: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | line starts with digit/letter garbage token | suspicious token(s): 1rg (letter/digit mix) :: 1rg 一 7.</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr">
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>814</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -708,24 +712,24 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: HOTEL ，</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: -â‚¬And Commercial Advertiser,</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •.</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 7</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -753,7 +757,7 @@
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: N.B.As the Messrs. Pannerâ€™s engage-</t>
+          <t>L1126: abbreviation/spacing may be garbled :: N.B.As the Messrs. Panner’s engage-</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -795,12 +799,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They would say â€” It is only Lady</t>
+          <t>L198: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FREDERICK STOBBS. â€” /_____</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -€And Commercial Advertiser,</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -812,7 +816,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: n</t>
+          <t>L5: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -846,12 +850,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -874,12 +878,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Alice.â€™ Yet I cannot tell how I shrink</t>
+          <t>L251: stray/suspicious non-ASCII glyph(s): U+5B66 CJK UNIFIED IDEOGRAPH-5B66, U+79C1 CJK UNIFIED IDEOGRAPH-79C1, U+85CF CJK UNIFIED IDEOGRAPH-85CF, U+9C7C CJK UNIFIED IDEOGRAPH-9C7C :: 学 私 藏 鱼</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ountryâ€”a record, the like of which</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -891,7 +895,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L117: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -945,12 +949,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER, U+00B1 PLUS-MINUS SIGN :: å­¦ ç§� è—� é±¼</t>
+          <t>L252: stray/suspicious non-ASCII glyph(s): U+4E3E CJK UNIFIED IDEOGRAPH-4E3E, U+6559 CJK UNIFIED IDEOGRAPH-6559, U+84C4 CJK UNIFIED IDEOGRAPH-84C4, U+9C7C CJK UNIFIED IDEOGRAPH-9C7C :: 举 教 蓄 鱼</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: e digestive organÃ© are restored to their</t>
+          <t>L208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: ending 31st December, on such of •• said</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -962,13 +966,13 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 0</t>
+          <t>L144: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: binâ€™s, Pinet, Castillonâ€™s, &amp;e..</t>
+          <t>L804: punctuation artifact: repeated periods :: bin’s, Pinet, Castillon’s, &amp;e..</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -1016,12 +1020,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+2022 BULLET, U+2122 TRADE MARK SIGN, U+00B1 PLUS-MINUS SIGN :: ä¸¾ æ•™ è“„ é±¼</t>
+          <t>L276: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | line starts with digit/letter garbage token | suspicious token(s): 1rg (letter/digit mix) :: 1rg 一 7.</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: :the patientâ€™s sy stem,</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: Â«</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1087,12 +1091,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | line starts with digit/letter garbage token | suspicious token(s): 1rg (letter/digit mix) :: 1rg ä¸€ 7.</t>
+          <t>L656: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | suspicious token(s): DrsrnPata (odd internal casing) :: DrsrnPata 一 No peréon with thie distres</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: wayâ€™s Pills are the best remedy</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: 1</t>
+          <t>L153: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1158,12 +1162,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Streets.â€” Near Ihe Post Office.</t>
+          <t>L690: stray/suspicious non-ASCII glyph(s): U+53D1 CJK UNIFIED IDEOGRAPH-53D1 | isolated marker/symbol line :: 发</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: pass the housekeeperâ€™s door, and she</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •There la considerable saving by taking</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1175,7 +1179,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: C</t>
+          <t>L157: isolated marker/symbol line :: «</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1183,7 +1187,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L421: line starts with punctuation glued to text :: ** And the wind. Lady Alice, was, meet all the ghosts in or out of Hades,</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1201,12 +1205,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1225,12 +1229,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L430: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: rh Ã¦ a. Dysen'ery. iping ini the Bowels. Aci.</t>
+          <t>L693: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sleeps but lightly.â€™</t>
+          <t>L507: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: commends i self as the only relinb • prepara-</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1242,7 +1246,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L277: isolated marker/symbol line :: 9</t>
+          <t>L169: isolated marker/symbol line :: ‘s</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1250,7 +1254,7 @@
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L739: line starts with punctuation glued to text :: -_choice Paintings, Sculp- tended eyes, as if they were the gates</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •There la considerable saving by taking</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1292,12 +1296,12 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L515: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Then, with a curling lipâ€”â€”</t>
+          <t>L763: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Are we near the housekeeperâ€™s</t>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: system subject to ■ return of the disease—</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1309,7 +1313,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L170: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1317,7 +1321,7 @@
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
+          <t>L421: line starts with punctuation glued to text :: ** And the wind. Lady Alice, was, meet all the ghosts in or out of Hades,</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1335,12 +1339,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1359,12 +1363,12 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L553: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI knew not whom I should rouse,</t>
+          <t>L790: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: PORTERS-Bridges, Hibbert's ， and Guin-</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They would sayâ€”-It is only Lady</t>
+          <t>L753: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1376,7 +1380,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: I</t>
+          <t>L275: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1384,7 +1388,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
+          <t>L739: line starts with punctuation glued to text :: -_choice Paintings, Sculp- tended eyes, as if they were the gates</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1426,12 +1430,12 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œi</t>
+          <t>L802: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: ALSO, 一</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Alice.â€™ Yet I cannot tell how I shrink</t>
+          <t>L939: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■ January, 1860, at which time the books will</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1443,13 +1447,17 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: C</t>
+          <t>L277: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>L753: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
+        </is>
+      </c>
       <c r="T13" s="1" t="inlineStr"/>
       <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr"/>
@@ -1470,7 +1478,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1489,12 +1497,12 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: did. And I hear it now â€” l hear it</t>
+          <t>L815: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from being seen by them. Noâ€”I will</t>
+          <t>L1156: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1506,13 +1514,17 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L724: isolated marker/symbol line :: 00</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
+        </is>
+      </c>
       <c r="T14" s="1" t="inlineStr"/>
       <c r="U14" s="1" t="inlineStr"/>
       <c r="V14" s="1" t="inlineStr"/>
@@ -1552,30 +1564,30 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: head â€”</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L1004: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L175: isolated marker/symbol line :: 66</t>
+          <t>L174: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L840: isolated marker/symbol line :: *</t>
+          <t>L398: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1615,24 +1627,20 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L590: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tle did I think then what memories â€”</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜s</t>
-        </is>
-      </c>
+          <t>L1050: stray/suspicious non-ASCII glyph(s): U+6D77 CJK UNIFIED IDEOGRAPH-6D77 | isolated marker/symbol line :: 海</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L196: symbol-only separator/garbage line :: 19100</t>
+          <t>L175: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L1031: isolated marker/symbol line :: ^1</t>
+          <t>L402: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1678,24 +1686,20 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L605: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: that I might take it back; adding â€”" I</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PACAUDâ€™S NEW Bl</t>
-        </is>
-      </c>
+          <t>L1057: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L197: isolated marker/symbol line :: X</t>
+          <t>L196: symbol-only separator/garbage line :: 19100</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L1092: isolated marker/symbol line :: M</t>
+          <t>L724: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1727,26 +1731,18 @@
           <t>L400: suspicious token(s): M0 (letter/digit mix) :: M0</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dicale:â€” A poor woman at Verneuil</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ending 31st December, on such of â€¢â€¢ said</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L199: isolated marker/symbol line :: -</t>
+          <t>L197: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L1100: isolated marker/symbol line :: a</t>
+          <t>L840: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1778,26 +1774,18 @@
           <t>L468: suspicious token(s): AMENT5 (letter/digit mix) :: AMENT5</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L656: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN | suspicious token(s): DrsrnPata (odd internal casing) :: DrsrnPata ä¸€ No perÃ©on with thie distres</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. Dâ€”The Certificates of the Shares in the</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L200: isolated marker/symbol line :: 4</t>
+          <t>L198: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L1102: isolated marker/symbol line :: 99</t>
+          <t>L1031: isolated marker/symbol line :: ^1</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1829,26 +1817,18 @@
           <t>L525: suspicious token(s): 1y (letter/digit mix) :: compa 1y each bottle Prepared by</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): MEaCURal (odd internal casing) :: MEaCURal Diseases.â€” Xerer filla to era-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€” pany of Canada,â€� as decided at a General</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L203: isolated marker/symbol line :: B</t>
+          <t>L199: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L1107: isolated marker/symbol line :: 8</t>
+          <t>L1092: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1877,29 +1857,21 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not â€ž</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�‘</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: - "How did I come here?â€� headâ€”</t>
-        </is>
-      </c>
+          <t>L735: suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not „</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L207: isolated marker/symbol line :: " T</t>
+          <t>L200: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L1116: isolated marker/symbol line :: a</t>
+          <t>L1100: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1923,7 +1895,7 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | line starts with digit/letter garbage token | suspicious token(s): 1rg (letter/digit mix) :: 1rg ä¸€ 7.</t>
+          <t>L276: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | line starts with digit/letter garbage token | suspicious token(s): 1rg (letter/digit mix) :: 1rg 一 7.</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr">
@@ -1931,26 +1903,18 @@
           <t>L772: suspicious token(s): LiverComplaint (odd internal casing) :: suffering from Consumption, LiverComplaint, tures. Outlines,</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L693: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: -â€œ I carried you.â€� â€œ Ah, yes! I am right at last; this</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L211: isolated marker/symbol line :: r</t>
+          <t>L203: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1102: isolated marker/symbol line :: 99</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1982,26 +1946,18 @@
           <t>L842: suspicious token(s): FISH11 (letter/digit mix) :: FISH ! FISH11 FISH II</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L281: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ST. NORBERT Dâ€™ARTHABASKA,</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L214: isolated marker/symbol line :: o</t>
+          <t>L207: isolated marker/symbol line :: " T</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1107: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -2033,26 +1989,18 @@
           <t>L906: suspicious token(s): 350de (letter/digit mix) :: 350de do</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ALSO, ä¸€</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Then, with a curling lipâ€” is the haunted room: I know my way</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L217: isolated marker/symbol line :: 1</t>
+          <t>L211: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L1146: isolated marker/symbol line :: -</t>
+          <t>L1116: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2084,26 +2032,18 @@
           <t>L954: suspicious token(s): CommissionAgent (odd internal casing) :: CommissionAgent,</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L875: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Shakespeare and his Friends.â€� Second: A</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " Where did you find me, pray ?" now.â€�</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L232: isolated marker/symbol line :: 1</t>
+          <t>L214: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L1148: isolated marker/symbol line :: 1</t>
+          <t>L1136: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2135,26 +2075,18 @@
           <t>L1016: suspicious token(s): ICommission (odd internal casing) :: ICommission Agent.</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L935: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œIdo not hear it," she said, after a</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L307: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: to go to it.â€� Ity and mustiness, I could not tell. Lit-</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L266: isolated marker/symbol line :: p</t>
+          <t>L217: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L1152: isolated marker/symbol line :: &amp;</t>
+          <t>L1138: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2186,26 +2118,18 @@
           <t>L1024: suspicious token(s): S3 (letter/digit mix) :: stead of S3, in order to defray extra postage,</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L948: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: you â€” you could not help it. I will</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L309: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Tis impossible. I see. Your the did I think then what memoriesâ€”</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L279: isolated marker/symbol line :: .</t>
+          <t>L232: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L1154: isolated marker/symbol line :: #</t>
+          <t>L1146: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2237,26 +2161,18 @@
           <t>L1048: suspicious token(s): inNew (odd internal casing) :: the heaviest ship-owners inNew Eng-</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L962: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: reviving, she went on through berâ€”would ere long find their being and</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L280: isolated marker/symbol line :: .</t>
+          <t>L266: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L1156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1148: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2288,26 +2204,18 @@
           <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L1004: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 4</t>
+          <t>L279: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L1158: isolated marker/symbol line :: 1</t>
+          <t>L1152: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2339,24 +2247,20 @@
           <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L1025: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 225 â€œ0</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CAUTION â€”None are genome unless</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L336: isolated marker/symbol line :: H</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="inlineStr"/>
+          <t>L280: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>L1154: isolated marker/symbol line :: #</t>
+        </is>
+      </c>
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr"/>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2387,19 +2291,19 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Sold at the Manufactories of Professor</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L342: isolated marker/symbol line :: &lt;</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr"/>
+          <t>L318: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>L1156: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr"/>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2426,19 +2330,19 @@
       </c>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L388: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢There la considerable saving by taking</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L343: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr"/>
+          <t>L336: isolated marker/symbol line :: H</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>L1158: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr"/>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2465,16 +2369,12 @@
       </c>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Why did you not leave me where to forsake it never, never moreâ€”the</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L388: isolated marker/symbol line :: 000</t>
+          <t>L342: isolated marker/symbol line :: &lt;</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2504,16 +2404,12 @@
       </c>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: terrible moon might have distorted that I might take it back; addingâ€”"I</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: 78</t>
+          <t>L343: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2543,16 +2439,12 @@
       </c>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: DR. EATONâ€™S</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L409: isolated marker/symbol line :: 0</t>
+          <t>L388: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2582,16 +2474,12 @@
       </c>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: commends i self as the only relinb â€¢ prepara-</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L456: isolated marker/symbol line :: P</t>
+          <t>L402: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2621,16 +2509,12 @@
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L513: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: relieving pain, it has no equalâ€”being an anti</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L464: isolated marker/symbol line :: -</t>
+          <t>L409: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2660,16 +2544,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: take n ne but Dr. Estonâ€™s INFANTI E COR-</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L473: isolated marker/symbol line :: 1</t>
+          <t>L456: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2694,21 +2574,17 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>L656: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN | suspicious token(s): DrsrnPata (odd internal casing) :: DrsrnPata ä¸€ No perÃ©on with thie distres</t>
+          <t>L656: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | suspicious token(s): DrsrnPata (odd internal casing) :: DrsrnPata 一 No peréon with thie distres</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L541: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Streets.â€”Near the Post Office.</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L487: isolated marker/symbol line :: 4</t>
+          <t>L464: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2733,21 +2609,17 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): MEaCURal (odd internal casing) :: MEaCURal Diseases.â€” Xerer filla to era-</t>
+          <t>L666: suspicious token(s): MEaCURal (odd internal casing) :: MEaCURal Diseases.— Xerer filla to era-</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: did. And I hear it nowâ€”I hear it markable cure ofa case</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L496: isolated marker/symbol line :: S</t>
+          <t>L473: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2777,16 +2649,12 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: FFATâ€™S</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L520: isolated marker/symbol line :: 66</t>
+          <t>L487: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2816,16 +2684,12 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: FENDTâ€™S</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L543: isolated marker/symbol line :: '</t>
+          <t>L496: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2855,16 +2719,12 @@
       </c>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L664: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LADIESâ€™ UNDERCLOTHING,</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L572: isolated marker/symbol line :: 4</t>
+          <t>L520: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2894,16 +2754,12 @@
       </c>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™ MORNING &amp; BREAKFAST</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L573: isolated marker/symbol line :: E</t>
+          <t>L543: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2933,16 +2789,12 @@
       </c>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 211 and 23 Notre Dame â€” al</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L640: isolated marker/symbol line :: P</t>
+          <t>L566: isolated marker/symbol line :: “i</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2972,16 +2824,12 @@
       </c>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Complaints â€”In the south and west, where</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: B</t>
+          <t>L572: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -3011,16 +2859,12 @@
       </c>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DYSPEPSIA â€”No person with this distres-</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L644: isolated marker/symbol line :: W</t>
+          <t>L573: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -3050,16 +2894,12 @@
       </c>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to â– return of the diseaseâ€”</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L645: isolated marker/symbol line :: 4</t>
+          <t>L640: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3089,16 +2929,12 @@
       </c>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L704: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a cure by these medicines to permanent. â€”</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L646: isolated marker/symbol line :: 4</t>
+          <t>L642: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3128,16 +2964,12 @@
       </c>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lockjaw.â€”The following very re-</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�‘</t>
+          <t>L644: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3167,16 +2999,12 @@
       </c>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The angry glow faded from her face, dicaleâ€”A poor woman at Verneuil</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L691: isolated marker/symbol line :: .</t>
+          <t>L645: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3206,16 +3034,12 @@
       </c>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: One Year. Third - A fire. Season Admission her, and rising from the couch. â€œI do!</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L693: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L646: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3245,16 +3069,12 @@
       </c>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not â€ž</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L694: isolated marker/symbol line :: 0</t>
+          <t>L690: stray/suspicious non-ASCII glyph(s): U+53D1 CJK UNIFIED IDEOGRAPH-53D1 | isolated marker/symbol line :: 发</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3284,16 +3104,12 @@
       </c>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and Foreign Artists. | â€œ I do not hear it,â€� she said, after a</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L704: isolated marker/symbol line :: 103</t>
+          <t>L691: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3323,16 +3139,12 @@
       </c>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: The beautiful Engraving, Which every Sub- â€žit must be now.â€� Then</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L730: isolated marker/symbol line :: -</t>
+          <t>L693: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3362,16 +3174,12 @@
       </c>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 4. Shakspeare and his Friends,â€� turning towards me. she laid her hand</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L745: isolated marker/symbol line :: . 0</t>
+          <t>L694: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3401,16 +3209,12 @@
       </c>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L753: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L746: isolated marker/symbol line :: b</t>
+          <t>L704: isolated marker/symbol line :: 103</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3436,16 +3240,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: J HOWARD MARCH &amp; CO.â€™s MADEI-</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L730: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3471,16 +3271,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L789: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: JUL S ROBIN &amp; CO.â€™S COGNAC BRAN-</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 8</t>
+          <t>L745: isolated marker/symbol line :: . 0</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3506,16 +3302,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L792: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OFFLEY. CE AMP &amp; co.â€™s PORT WIN S</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L811: isolated marker/symbol line :: 3</t>
+          <t>L746: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3541,16 +3333,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L794: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WM YOUNGER &amp; CO.â€™S EDINBURGH</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L813: isolated marker/symbol line :: 55</t>
+          <t>L763: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3576,16 +3364,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: for sale on very advantageous terms:â€”</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L830: isolated marker/symbol line :: 2</t>
+          <t>L809: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3611,16 +3395,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BRANDIES-Martellâ€™s, Hennesseyâ€™s, Ro-</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: 2</t>
+          <t>L811: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3646,16 +3426,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: binâ€™s, Pinet, Castillonâ€™s, &amp;e..</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L957: isolated marker/symbol line :: '</t>
+          <t>L813: isolated marker/symbol line :: 55</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3681,16 +3457,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GINSâ€”Holland and English, of best brands</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L970: isolated marker/symbol line :: 2</t>
+          <t>L815: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3716,16 +3488,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L812: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ALES Bassâ€™, Allsoppâ€™s and Youngerâ€™s, in</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L1002: isolated marker/symbol line :: 1</t>
+          <t>L830: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3751,16 +3519,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L815: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PORTERSâ€”Bridgeâ€™s, Hibbertâ€™s, and Guin-</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L1004: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L866: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3786,16 +3550,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: nessâ€™, in wood and bottle</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L1005: isolated marker/symbol line :: 000</t>
+          <t>L957: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3821,16 +3581,12 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WHISKIESâ€”SCOTCH and IRISH, of the</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L1006: isolated marker/symbol line :: 0</t>
+          <t>L962: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3856,16 +3612,12 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L822: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: PORT WINESâ€”Offley &amp; Co â€˜s. Spademan a</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L1007: isolated marker/symbol line :: ;</t>
+          <t>L970: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3891,16 +3643,12 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: SHERRIESâ€” Crump. Suter &amp; Co.â€™s, Do</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L1028: isolated marker/symbol line :: 350</t>
+          <t>L1002: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3926,16 +3674,12 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: meeq.â€˜s, Pemartinâ€™s &amp;c.</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L1029: isolated marker/symbol line :: "</t>
+          <t>L1004: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3961,16 +3705,12 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CHAMPAGNESâ€”Meet &amp; Chandonâ€™s, and</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: d</t>
+          <t>L1005: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3996,16 +3736,12 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CLARETSâ€”Of various ages, in wood and</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L1033: isolated marker/symbol line :: 15</t>
+          <t>L1006: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4031,16 +3767,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No. I Gibâ€™d Arichat,</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: 75</t>
+          <t>L1007: isolated marker/symbol line :: ;</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4066,16 +3798,12 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MERCURAL DISEASES â€”Never fails to era-</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L1037: isolated marker/symbol line :: 200</t>
+          <t>L1025: symbol-only separator/garbage line :: 225 “0</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4101,16 +3829,12 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Palpitation of the Heart, Painterâ€™s Cholic.</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L1038: isolated marker/symbol line :: .</t>
+          <t>L1028: isolated marker/symbol line :: 350</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4136,16 +3860,12 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L883: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: I'll ES â€”The original Proprietor of these</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L1039: isolated marker/symbol line :: 8</t>
+          <t>L1029: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4171,16 +3891,12 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L912: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: youâ€”you could not help it. I will</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L1045: isolated marker/symbol line :: 30</t>
+          <t>L1030: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4206,16 +3922,12 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: duties of Customs;â€� the duty, heret fore im-</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L1046: isolated marker/symbol line :: .</t>
+          <t>L1033: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4241,16 +3953,12 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER, U+02DC SMALL TILDE :: %â€œ Scottsâ€� Brand, Choiâ€˜e.</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L1047: isolated marker/symbol line :: -</t>
+          <t>L1034: isolated marker/symbol line :: 75</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4276,16 +3984,12 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
       <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L1064: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: this night or morningâ€”hichever it</t>
-        </is>
-      </c>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L1049: isolated marker/symbol line :: '</t>
+          <t>L1037: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4311,16 +4015,12 @@
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
       <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L1065: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI It is past midnight, but not morn-</t>
-        </is>
-      </c>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L1051: isolated marker/symbol line :: 7</t>
+          <t>L1038: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4346,16 +4046,12 @@
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
       <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L1066: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ofthe papers from the Reading Tables of the ing yet,â€� she replied ;" I always know</t>
-        </is>
-      </c>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L1052: isolated marker/symbol line :: 2</t>
+          <t>L1039: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4381,16 +4077,12 @@
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
       <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L1070: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ There is; but we should have to with her riding-master.</t>
-        </is>
-      </c>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L1053: isolated marker/symbol line :: 27</t>
+          <t>L1045: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4416,16 +4108,12 @@
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
       <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L1082: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ALSO,â€”</t>
-        </is>
-      </c>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L1054: isolated marker/symbol line :: 4</t>
+          <t>L1046: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4451,16 +4139,12 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
       <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CO.â€™</t>
-        </is>
-      </c>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L1058: isolated marker/symbol line :: C</t>
+          <t>L1047: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4486,16 +4170,12 @@
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
       <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: N.B.As the Messrs. Pannerâ€™s engage-</t>
-        </is>
-      </c>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L1059: isolated marker/symbol line :: A</t>
+          <t>L1049: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4521,16 +4201,12 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
       <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L1060: isolated marker/symbol line :: e</t>
+          <t>L1050: stray/suspicious non-ASCII glyph(s): U+6D77 CJK UNIFIED IDEOGRAPH-6D77 | isolated marker/symbol line :: 海</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4556,16 +4232,12 @@
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
       <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L1061: isolated marker/symbol line :: n</t>
+          <t>L1051: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4591,16 +4263,12 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
       <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L1062: isolated marker/symbol line :: +</t>
+          <t>L1052: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4615,6 +4283,254 @@
       <c r="X91" s="1" t="inlineStr"/>
       <c r="Y91" s="1" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr"/>
+      <c r="B92" s="1" t="inlineStr"/>
+      <c r="C92" s="1" t="inlineStr"/>
+      <c r="D92" s="1" t="inlineStr"/>
+      <c r="E92" s="1" t="inlineStr"/>
+      <c r="F92" s="1" t="inlineStr"/>
+      <c r="G92" s="1" t="inlineStr"/>
+      <c r="H92" s="1" t="inlineStr"/>
+      <c r="I92" s="1" t="inlineStr"/>
+      <c r="J92" s="1" t="inlineStr"/>
+      <c r="K92" s="1" t="inlineStr"/>
+      <c r="L92" s="1" t="inlineStr"/>
+      <c r="M92" s="1" t="inlineStr"/>
+      <c r="N92" s="1" t="inlineStr">
+        <is>
+          <t>L1053: isolated marker/symbol line :: 27</t>
+        </is>
+      </c>
+      <c r="O92" s="1" t="inlineStr"/>
+      <c r="P92" s="1" t="inlineStr"/>
+      <c r="Q92" s="1" t="inlineStr"/>
+      <c r="R92" s="1" t="inlineStr"/>
+      <c r="S92" s="1" t="inlineStr"/>
+      <c r="T92" s="1" t="inlineStr"/>
+      <c r="U92" s="1" t="inlineStr"/>
+      <c r="V92" s="1" t="inlineStr"/>
+      <c r="W92" s="1" t="inlineStr"/>
+      <c r="X92" s="1" t="inlineStr"/>
+      <c r="Y92" s="1" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr"/>
+      <c r="B93" s="1" t="inlineStr"/>
+      <c r="C93" s="1" t="inlineStr"/>
+      <c r="D93" s="1" t="inlineStr"/>
+      <c r="E93" s="1" t="inlineStr"/>
+      <c r="F93" s="1" t="inlineStr"/>
+      <c r="G93" s="1" t="inlineStr"/>
+      <c r="H93" s="1" t="inlineStr"/>
+      <c r="I93" s="1" t="inlineStr"/>
+      <c r="J93" s="1" t="inlineStr"/>
+      <c r="K93" s="1" t="inlineStr"/>
+      <c r="L93" s="1" t="inlineStr"/>
+      <c r="M93" s="1" t="inlineStr"/>
+      <c r="N93" s="1" t="inlineStr">
+        <is>
+          <t>L1054: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O93" s="1" t="inlineStr"/>
+      <c r="P93" s="1" t="inlineStr"/>
+      <c r="Q93" s="1" t="inlineStr"/>
+      <c r="R93" s="1" t="inlineStr"/>
+      <c r="S93" s="1" t="inlineStr"/>
+      <c r="T93" s="1" t="inlineStr"/>
+      <c r="U93" s="1" t="inlineStr"/>
+      <c r="V93" s="1" t="inlineStr"/>
+      <c r="W93" s="1" t="inlineStr"/>
+      <c r="X93" s="1" t="inlineStr"/>
+      <c r="Y93" s="1" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr"/>
+      <c r="B94" s="1" t="inlineStr"/>
+      <c r="C94" s="1" t="inlineStr"/>
+      <c r="D94" s="1" t="inlineStr"/>
+      <c r="E94" s="1" t="inlineStr"/>
+      <c r="F94" s="1" t="inlineStr"/>
+      <c r="G94" s="1" t="inlineStr"/>
+      <c r="H94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr"/>
+      <c r="J94" s="1" t="inlineStr"/>
+      <c r="K94" s="1" t="inlineStr"/>
+      <c r="L94" s="1" t="inlineStr"/>
+      <c r="M94" s="1" t="inlineStr"/>
+      <c r="N94" s="1" t="inlineStr">
+        <is>
+          <t>L1057: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O94" s="1" t="inlineStr"/>
+      <c r="P94" s="1" t="inlineStr"/>
+      <c r="Q94" s="1" t="inlineStr"/>
+      <c r="R94" s="1" t="inlineStr"/>
+      <c r="S94" s="1" t="inlineStr"/>
+      <c r="T94" s="1" t="inlineStr"/>
+      <c r="U94" s="1" t="inlineStr"/>
+      <c r="V94" s="1" t="inlineStr"/>
+      <c r="W94" s="1" t="inlineStr"/>
+      <c r="X94" s="1" t="inlineStr"/>
+      <c r="Y94" s="1" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr"/>
+      <c r="B95" s="1" t="inlineStr"/>
+      <c r="C95" s="1" t="inlineStr"/>
+      <c r="D95" s="1" t="inlineStr"/>
+      <c r="E95" s="1" t="inlineStr"/>
+      <c r="F95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr"/>
+      <c r="H95" s="1" t="inlineStr"/>
+      <c r="I95" s="1" t="inlineStr"/>
+      <c r="J95" s="1" t="inlineStr"/>
+      <c r="K95" s="1" t="inlineStr"/>
+      <c r="L95" s="1" t="inlineStr"/>
+      <c r="M95" s="1" t="inlineStr"/>
+      <c r="N95" s="1" t="inlineStr">
+        <is>
+          <t>L1058: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
+      <c r="O95" s="1" t="inlineStr"/>
+      <c r="P95" s="1" t="inlineStr"/>
+      <c r="Q95" s="1" t="inlineStr"/>
+      <c r="R95" s="1" t="inlineStr"/>
+      <c r="S95" s="1" t="inlineStr"/>
+      <c r="T95" s="1" t="inlineStr"/>
+      <c r="U95" s="1" t="inlineStr"/>
+      <c r="V95" s="1" t="inlineStr"/>
+      <c r="W95" s="1" t="inlineStr"/>
+      <c r="X95" s="1" t="inlineStr"/>
+      <c r="Y95" s="1" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr"/>
+      <c r="B96" s="1" t="inlineStr"/>
+      <c r="C96" s="1" t="inlineStr"/>
+      <c r="D96" s="1" t="inlineStr"/>
+      <c r="E96" s="1" t="inlineStr"/>
+      <c r="F96" s="1" t="inlineStr"/>
+      <c r="G96" s="1" t="inlineStr"/>
+      <c r="H96" s="1" t="inlineStr"/>
+      <c r="I96" s="1" t="inlineStr"/>
+      <c r="J96" s="1" t="inlineStr"/>
+      <c r="K96" s="1" t="inlineStr"/>
+      <c r="L96" s="1" t="inlineStr"/>
+      <c r="M96" s="1" t="inlineStr"/>
+      <c r="N96" s="1" t="inlineStr">
+        <is>
+          <t>L1059: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
+      <c r="O96" s="1" t="inlineStr"/>
+      <c r="P96" s="1" t="inlineStr"/>
+      <c r="Q96" s="1" t="inlineStr"/>
+      <c r="R96" s="1" t="inlineStr"/>
+      <c r="S96" s="1" t="inlineStr"/>
+      <c r="T96" s="1" t="inlineStr"/>
+      <c r="U96" s="1" t="inlineStr"/>
+      <c r="V96" s="1" t="inlineStr"/>
+      <c r="W96" s="1" t="inlineStr"/>
+      <c r="X96" s="1" t="inlineStr"/>
+      <c r="Y96" s="1" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr"/>
+      <c r="B97" s="1" t="inlineStr"/>
+      <c r="C97" s="1" t="inlineStr"/>
+      <c r="D97" s="1" t="inlineStr"/>
+      <c r="E97" s="1" t="inlineStr"/>
+      <c r="F97" s="1" t="inlineStr"/>
+      <c r="G97" s="1" t="inlineStr"/>
+      <c r="H97" s="1" t="inlineStr"/>
+      <c r="I97" s="1" t="inlineStr"/>
+      <c r="J97" s="1" t="inlineStr"/>
+      <c r="K97" s="1" t="inlineStr"/>
+      <c r="L97" s="1" t="inlineStr"/>
+      <c r="M97" s="1" t="inlineStr"/>
+      <c r="N97" s="1" t="inlineStr">
+        <is>
+          <t>L1060: isolated marker/symbol line :: e</t>
+        </is>
+      </c>
+      <c r="O97" s="1" t="inlineStr"/>
+      <c r="P97" s="1" t="inlineStr"/>
+      <c r="Q97" s="1" t="inlineStr"/>
+      <c r="R97" s="1" t="inlineStr"/>
+      <c r="S97" s="1" t="inlineStr"/>
+      <c r="T97" s="1" t="inlineStr"/>
+      <c r="U97" s="1" t="inlineStr"/>
+      <c r="V97" s="1" t="inlineStr"/>
+      <c r="W97" s="1" t="inlineStr"/>
+      <c r="X97" s="1" t="inlineStr"/>
+      <c r="Y97" s="1" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr"/>
+      <c r="B98" s="1" t="inlineStr"/>
+      <c r="C98" s="1" t="inlineStr"/>
+      <c r="D98" s="1" t="inlineStr"/>
+      <c r="E98" s="1" t="inlineStr"/>
+      <c r="F98" s="1" t="inlineStr"/>
+      <c r="G98" s="1" t="inlineStr"/>
+      <c r="H98" s="1" t="inlineStr"/>
+      <c r="I98" s="1" t="inlineStr"/>
+      <c r="J98" s="1" t="inlineStr"/>
+      <c r="K98" s="1" t="inlineStr"/>
+      <c r="L98" s="1" t="inlineStr"/>
+      <c r="M98" s="1" t="inlineStr"/>
+      <c r="N98" s="1" t="inlineStr">
+        <is>
+          <t>L1061: isolated marker/symbol line :: n</t>
+        </is>
+      </c>
+      <c r="O98" s="1" t="inlineStr"/>
+      <c r="P98" s="1" t="inlineStr"/>
+      <c r="Q98" s="1" t="inlineStr"/>
+      <c r="R98" s="1" t="inlineStr"/>
+      <c r="S98" s="1" t="inlineStr"/>
+      <c r="T98" s="1" t="inlineStr"/>
+      <c r="U98" s="1" t="inlineStr"/>
+      <c r="V98" s="1" t="inlineStr"/>
+      <c r="W98" s="1" t="inlineStr"/>
+      <c r="X98" s="1" t="inlineStr"/>
+      <c r="Y98" s="1" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr"/>
+      <c r="B99" s="1" t="inlineStr"/>
+      <c r="C99" s="1" t="inlineStr"/>
+      <c r="D99" s="1" t="inlineStr"/>
+      <c r="E99" s="1" t="inlineStr"/>
+      <c r="F99" s="1" t="inlineStr"/>
+      <c r="G99" s="1" t="inlineStr"/>
+      <c r="H99" s="1" t="inlineStr"/>
+      <c r="I99" s="1" t="inlineStr"/>
+      <c r="J99" s="1" t="inlineStr"/>
+      <c r="K99" s="1" t="inlineStr"/>
+      <c r="L99" s="1" t="inlineStr"/>
+      <c r="M99" s="1" t="inlineStr"/>
+      <c r="N99" s="1" t="inlineStr">
+        <is>
+          <t>L1062: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
+      <c r="O99" s="1" t="inlineStr"/>
+      <c r="P99" s="1" t="inlineStr"/>
+      <c r="Q99" s="1" t="inlineStr"/>
+      <c r="R99" s="1" t="inlineStr"/>
+      <c r="S99" s="1" t="inlineStr"/>
+      <c r="T99" s="1" t="inlineStr"/>
+      <c r="U99" s="1" t="inlineStr"/>
+      <c r="V99" s="1" t="inlineStr"/>
+      <c r="W99" s="1" t="inlineStr"/>
+      <c r="X99" s="1" t="inlineStr"/>
+      <c r="Y99" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
